--- a/tools/config-xlsx/chest.xlsx
+++ b/tools/config-xlsx/chest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B3">
         <v>0.03</v>
@@ -453,7 +453,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B4">
         <v>0.03</v>
@@ -468,16 +468,50 @@
         <v>final_default</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B5">
+        <v>0.03</v>
+      </c>
+      <c r="C5">
+        <v>0.35</v>
+      </c>
+      <c r="D5" t="str">
+        <v>mob_default</v>
+      </c>
+      <c r="E5" t="str">
+        <v>final_default</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B6">
+        <v>0.03</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>mob_default</v>
+      </c>
+      <c r="E6" t="str">
+        <v>final_boss</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -556,9 +590,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>final_boss</v>
+      </c>
+      <c r="B8" t="str">
+        <v>normal</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>final_boss</v>
+      </c>
+      <c r="B9" t="str">
+        <v>boss</v>
+      </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>final_boss</v>
+      </c>
+      <c r="B10" t="str">
+        <v>chapter</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/config-xlsx/chest.xlsx
+++ b/tools/config-xlsx/chest.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Groups" sheetId="1" r:id="rId1"/>
     <sheet name="TypeWeights" sheetId="2" r:id="rId2"/>
+    <sheet name="Rewards" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -628,4 +629,131 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>chestType</v>
+      </c>
+      <c r="B1" t="str">
+        <v>equipmentRolls</v>
+      </c>
+      <c r="C1" t="str">
+        <v>forgeStoneMin</v>
+      </c>
+      <c r="D1" t="str">
+        <v>forgeStoneMax</v>
+      </c>
+      <c r="E1" t="str">
+        <v>gemCount</v>
+      </c>
+      <c r="F1" t="str">
+        <v>gemLevelMin</v>
+      </c>
+      <c r="G1" t="str">
+        <v>gemLevelMax</v>
+      </c>
+      <c r="H1" t="str">
+        <v>scrollMin</v>
+      </c>
+      <c r="I1" t="str">
+        <v>scrollMax</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>normal</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>boss</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>chapter</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+  </ignoredErrors>
+</worksheet>
 </file>